--- a/results/Int Task Remove ACC -1.0/Rando_8_permute.xlsx
+++ b/results/Int Task Remove ACC -1.0/Rando_8_permute.xlsx
@@ -440,347 +440,347 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6377491510280152</v>
+        <v>0.6287134017164416</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6402363859096827</v>
+        <v>0.6267004743074727</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6098110797387993</v>
+        <v>0.6220439545865428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6025099206695448</v>
+        <v>0.6174666606171233</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5977710340880138</v>
+        <v>0.619322183559435</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5970986622365395</v>
+        <v>0.6169944472171518</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.587782481685589</v>
+        <v>0.6313622292102206</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5875458514674214</v>
+        <v>0.6462772622093165</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5749168478621263</v>
+        <v>0.6441840620124737</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5694305518230648</v>
+        <v>0.6441840620124737</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5667848654383767</v>
+        <v>0.6441840620124737</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5662323792505314</v>
+        <v>0.6041330015391434</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5662323792505314</v>
+        <v>0.5938723941882502</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5588676999752201</v>
+        <v>0.6034585356149419</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5577231147237743</v>
+        <v>0.5991094955727813</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5539338901240041</v>
+        <v>0.6051899847481703</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5540912945906611</v>
+        <v>0.6051899847481703</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5537754386209833</v>
+        <v>0.6051899847481703</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5444978239094244</v>
+        <v>0.6071236864056289</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5420084949550298</v>
+        <v>0.6071236864056289</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5376292653643862</v>
+        <v>0.61189485660837</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5077981523298304</v>
+        <v>0.6058476980905547</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5077981523298304</v>
+        <v>0.5933291568216164</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.506532634378392</v>
+        <v>0.6006667876575353</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4982807662910133</v>
+        <v>0.6020553323816936</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5029414741573975</v>
+        <v>0.5751243355681742</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5238525353985544</v>
+        <v>0.5655725718354199</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5175406511868157</v>
+        <v>0.5547896678451643</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5203823078775526</v>
+        <v>0.567968016529214</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5058279789057074</v>
+        <v>0.5283464154710094</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5010161487908474</v>
+        <v>0.5464939987365761</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5120252126356348</v>
+        <v>0.546809854706254</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5039766441088499</v>
+        <v>0.5723763886319773</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5079972637449699</v>
+        <v>0.5838660421676445</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5083131197146478</v>
+        <v>0.5938086994761329</v>
       </c>
     </row>
     <row r="37">
@@ -790,537 +790,537 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5049950614784852</v>
+        <v>0.5938097465124964</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4855027345099696</v>
+        <v>0.5779096268013388</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4836836833343222</v>
+        <v>0.5599278242933378</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4855798661887527</v>
+        <v>0.5740849774712675</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4855798661887527</v>
+        <v>0.5617728768720138</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4882641184128325</v>
+        <v>0.545247327439682</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4796599225891115</v>
+        <v>0.5230436998076943</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4760677153317535</v>
+        <v>0.5089970089661214</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4780795957043589</v>
+        <v>0.5109328046963071</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.478867665074008</v>
+        <v>0.505488215605728</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4828914258192187</v>
+        <v>0.5011840236211403</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4882192703552595</v>
+        <v>0.4997996670424364</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4880212059764836</v>
+        <v>0.4984142634273688</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4931124202943568</v>
+        <v>0.5029529915573968</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5001832313636253</v>
+        <v>0.5029529915573968</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5090188222236959</v>
+        <v>0.4762689208196201</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4802738349102864</v>
+        <v>0.476261591565075</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4737576041015905</v>
+        <v>0.4883110605431327</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4599944856084852</v>
+        <v>0.4863398400826461</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4511119526181144</v>
+        <v>0.4976398055304461</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4511119526181144</v>
+        <v>0.4906993504884425</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.443492843506455</v>
+        <v>0.4910954792459942</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4452680936608928</v>
+        <v>0.4875158364249991</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4452680936608928</v>
+        <v>0.4881079354885995</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4641360379445978</v>
+        <v>0.4901458172642336</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5167223922686834</v>
+        <v>0.4775126255134841</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.524461387043972</v>
+        <v>0.4752662089954384</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5252505034499848</v>
+        <v>0.4641580257082328</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5147387818778946</v>
+        <v>0.4585904098449339</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5109506043144879</v>
+        <v>0.4600904639418127</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5032585516694995</v>
+        <v>0.4600904639418127</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4995475057848759</v>
+        <v>0.4901217354278714</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4940653978912688</v>
+        <v>0.4674436258171246</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5021963332786548</v>
+        <v>0.4681149506322355</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5057009384935939</v>
+        <v>0.4662793213808316</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4941289180973255</v>
+        <v>0.4853671433008868</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4934972061579699</v>
+        <v>0.4673394456989491</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4938870526973402</v>
+        <v>0.4755475127651184</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4897016993400181</v>
+        <v>0.4948532927548573</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4855549118220875</v>
+        <v>0.4888926892430974</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4855549118220875</v>
+        <v>0.4817271213829256</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4853182816039201</v>
+        <v>0.4733522265228272</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4654162144051263</v>
+        <v>0.4696828875866859</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4662751332353773</v>
+        <v>0.4853287519675558</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4670382482383613</v>
+        <v>0.4968997253274606</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4670382482383613</v>
+        <v>0.4974918243910611</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4696130851624477</v>
+        <v>0.4981183011485989</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5036255379149318</v>
+        <v>0.4974073634577328</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5004336475605797</v>
+        <v>0.4953099751154357</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.500591052027237</v>
+        <v>0.4953099751154357</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4999593400878812</v>
+        <v>0.5035117599634236</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5011028783029635</v>
+        <v>0.5053067293027087</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5011028783029635</v>
+        <v>0.4930468060155729</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4992494494333788</v>
+        <v>0.4930864188913281</v>
       </c>
     </row>
   </sheetData>
